--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108154</v>
+        <v>108158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108158</v>
+        <v>108179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108179</v>
+        <v>108180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108180</v>
+        <v>108185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108185</v>
+        <v>108188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108188</v>
+        <v>108194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108194</v>
+        <v>108195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108195</v>
+        <v>108207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108207</v>
+        <v>108208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108208</v>
+        <v>108211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108211</v>
+        <v>108213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26139-2022 artfynd.xlsx
+++ b/artfynd/A 26139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956994</v>
       </c>
       <c r="B2" t="n">
-        <v>108213</v>
+        <v>108217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
